--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486541_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486541_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0875</v>
+        <v>7.1684</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3497</v>
+        <v>6.4615</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7377</v>
+        <v>0.7069</v>
       </c>
       <c r="G2" t="n">
         <v>6.5563</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2484</v>
+        <v>1.3294</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2776</v>
+        <v>0.3894</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9708</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9347</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8079</v>
+        <v>4.8425</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9725</v>
+        <v>3.6372</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8354</v>
+        <v>1.2053</v>
       </c>
       <c r="G3" t="n">
         <v>4.9946</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5757</v>
+        <v>1.6103</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9542</v>
+        <v>0.6189</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>0.1952</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4439</v>
+        <v>3.9903</v>
       </c>
       <c r="E4" t="n">
-        <v>2.948</v>
+        <v>3.4636</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4959</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>3.9972</v>
@@ -766,13 +766,13 @@
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1215</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8099</v>
+        <v>-0.2944</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9314</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.981</v>
+        <v>3.4888</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5006</v>
+        <v>1.7927</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4804</v>
+        <v>1.6961</v>
       </c>
       <c r="G5" t="n">
         <v>2.9367</v>
@@ -844,13 +844,13 @@
         <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3032</v>
+        <v>0.2046</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.4614</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4503</v>
+        <v>0.666</v>
       </c>
       <c r="V5" t="n">
         <v>0.5649999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8931</v>
+        <v>1.9846</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0654</v>
+        <v>2.9104</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1724</v>
+        <v>-0.9258</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6548</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>0.418</v>
+        <v>0.5095</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2211</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1968</v>
+        <v>0.4434</v>
       </c>
       <c r="V6" t="n">
         <v>1.695</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>B. VIDARTE CANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6985</v>
+        <v>0.673</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5702</v>
+        <v>-0.1371</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2686</v>
+        <v>0.8101</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5788</v>
+        <v>-0.486</v>
       </c>
       <c r="H7" t="n">
-        <v>2.567</v>
+        <v>0.1946</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9881</v>
+        <v>-0.6805</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0706</v>
+        <v>-0.5991</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9558</v>
+        <v>0.146</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1147</v>
+        <v>-0.7451</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4917</v>
+        <v>0.1131</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6111</v>
+        <v>0.0486</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1029</v>
+        <v>0.0645</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.9151</v>
+        <v>0.435</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3501</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4045</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0791</v>
+        <v>0.2668</v>
       </c>
       <c r="U7" t="n">
-        <v>2.3254</v>
+        <v>0.262</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3698</v>
+        <v>0.1952</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>B. VIDARTE CANO</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3378</v>
+        <v>0.1966</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4723</v>
+        <v>1.9016</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8101</v>
+        <v>-1.705</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.486</v>
+        <v>-0.9697</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1946</v>
+        <v>1.0615</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6805</v>
+        <v>-2.0312</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5991</v>
+        <v>1.362</v>
       </c>
       <c r="K8" t="n">
-        <v>0.146</v>
+        <v>1.9923</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7451</v>
+        <v>-0.6303</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1131</v>
+        <v>-2.3318</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0486</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0645</v>
+        <v>-1.4009</v>
       </c>
       <c r="P8" t="n">
         <v>0.435</v>
@@ -1078,28 +1078,28 @@
         <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1935</v>
+        <v>0.9265</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.5396</v>
       </c>
       <c r="U8" t="n">
-        <v>0.262</v>
+        <v>0.3869</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1952</v>
+        <v>-0.1952</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0733</v>
+        <v>-0.7542</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9016</v>
+        <v>-2.129</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.8283</v>
+        <v>1.3748</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9697</v>
+        <v>1.5788</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0615</v>
+        <v>2.567</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0312</v>
+        <v>-0.9881</v>
       </c>
       <c r="J9" t="n">
-        <v>1.362</v>
+        <v>2.0706</v>
       </c>
       <c r="K9" t="n">
-        <v>1.9923</v>
+        <v>1.9558</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6303</v>
+        <v>0.1147</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3318</v>
+        <v>-0.4917</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9308999999999999</v>
+        <v>0.6111</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4009</v>
+        <v>-1.1029</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>-3.9151</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R9" t="n">
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8032</v>
+        <v>1.9518</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5396</v>
+        <v>0.5203</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2636</v>
+        <v>1.4315</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8225</v>
+        <v>-2.7723</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.302</v>
+        <v>-3.1902</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4795</v>
+        <v>0.4179</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8118</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3819</v>
+        <v>0.432</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.113</v>
+        <v>-0.0012</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4949</v>
+        <v>0.4332</v>
       </c>
       <c r="V10" t="n">
         <v>1.13</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1664</v>
+        <v>-3.5988</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1332</v>
+        <v>-3.2883</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0332</v>
+        <v>-0.3106</v>
       </c>
       <c r="G11" t="n">
         <v>-3.189</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1525</v>
+        <v>0.7201</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1526</v>
+        <v>-0.0024</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9999</v>
+        <v>0.7225</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6061</v>
+        <v>-6.1484</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6039</v>
+        <v>-4.4236</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0022</v>
+        <v>-1.7248</v>
       </c>
       <c r="G12" t="n">
         <v>-2.852</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5361</v>
+        <v>-0.0784</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8784</v>
+        <v>-0.6982</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3424</v>
+        <v>0.6198</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3904</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.728000000000003</v>
+        <v>9.070499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>6.656200000000003</v>
+        <v>6.998799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0715</v>
+        <v>2.0716</v>
       </c>
       <c r="G13" t="n">
         <v>9.100299999999999</v>
@@ -1468,13 +1468,13 @@
         <v>8.700000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>8.459900000000001</v>
+        <v>8.802300000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6009000000000003</v>
+        <v>0.9434999999999997</v>
       </c>
       <c r="U13" t="n">
-        <v>7.859000000000001</v>
+        <v>7.8589</v>
       </c>
       <c r="V13" t="n">
         <v>0.9555000000000002</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.0326</v>
+        <v>9.2883</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2655</v>
+        <v>6.3773</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7671</v>
+        <v>2.911</v>
       </c>
       <c r="G14" t="n">
         <v>6.5308</v>
@@ -1546,13 +1546,13 @@
         <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8478</v>
+        <v>-0.5921</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2209</v>
+        <v>-1.1092</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3731</v>
+        <v>0.517</v>
       </c>
       <c r="V14" t="n">
         <v>0.7395</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0385</v>
+        <v>2.6088</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9915</v>
+        <v>3.4385</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.953</v>
+        <v>-0.8297</v>
       </c>
       <c r="G15" t="n">
         <v>1.6483</v>
@@ -1624,13 +1624,13 @@
         <v>2.8276</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3923</v>
+        <v>-0.822</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4384</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0461</v>
+        <v>0.1694</v>
       </c>
       <c r="V15" t="n">
         <v>1.13</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3575</v>
+        <v>0.1447</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4</v>
+        <v>-1.2882</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0424</v>
+        <v>1.4329</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2757</v>
@@ -1702,13 +1702,13 @@
         <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7349</v>
+        <v>-1.2326</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2894</v>
+        <v>-1.1776</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4455</v>
+        <v>-0.055</v>
       </c>
       <c r="V16" t="n">
         <v>-0.7395</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4373</v>
+        <v>-0.3448</v>
       </c>
       <c r="E17" t="n">
         <v>-1.2</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7627</v>
+        <v>0.8552</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6035</v>
@@ -1780,13 +1780,13 @@
         <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4863</v>
+        <v>-0.3939</v>
       </c>
       <c r="T17" t="n">
         <v>-0.548</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4848</v>
+        <v>-0.8509</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2625</v>
+        <v>1.3219</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7473</v>
+        <v>-2.1728</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8378</v>
+        <v>-2.0207</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.5023</v>
+        <v>0.0487</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6646</v>
+        <v>-2.0694</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6599</v>
+        <v>1.3406</v>
       </c>
       <c r="K18" t="n">
-        <v>0.192</v>
+        <v>1.2441</v>
       </c>
       <c r="L18" t="n">
-        <v>2.4679</v>
+        <v>0.0964</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.4976</v>
+        <v>-3.3613</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6943</v>
+        <v>-1.1954</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8033</v>
+        <v>-2.1659</v>
       </c>
       <c r="P18" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.0451</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3218</v>
+        <v>-0.113</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2223</v>
+        <v>-0.2139</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.1009</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7276</v>
+        <v>-0.9446</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3219</v>
+        <v>-0.408</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0495</v>
+        <v>-0.5366</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0207</v>
+        <v>-0.8378</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0487</v>
+        <v>-1.5023</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.0694</v>
+        <v>0.6646</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3406</v>
+        <v>2.6599</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2441</v>
+        <v>0.192</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0964</v>
+        <v>2.4679</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.3613</v>
+        <v>-3.4976</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1954</v>
+        <v>-1.6943</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1659</v>
+        <v>-1.8033</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>3.0451</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0103</v>
+        <v>-0.7817</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2139</v>
+        <v>-0.8928</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2242</v>
+        <v>0.1111</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1952</v>
+        <v>-0.1952</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2458</v>
+        <v>-1.0789</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6373</v>
+        <v>-0.8608</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6086</v>
+        <v>-0.2181</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2457</v>
@@ -2014,13 +2014,13 @@
         <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9778</v>
+        <v>-0.8108</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6813</v>
+        <v>-0.9049</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2965</v>
+        <v>0.094</v>
       </c>
       <c r="V20" t="n">
         <v>1.3252</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7644</v>
+        <v>-2.2686</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1722</v>
+        <v>1.3957</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9366</v>
+        <v>-3.6643</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6602</v>
@@ -2092,13 +2092,13 @@
         <v>0.435</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.3485</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2963</v>
+        <v>-0.024</v>
       </c>
       <c r="V21" t="n">
         <v>-1.695</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2314</v>
+        <v>-6.7015</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8001</v>
+        <v>-5.0236</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4313</v>
+        <v>-1.6778</v>
       </c>
       <c r="G22" t="n">
         <v>-6.0849</v>
@@ -2170,13 +2170,13 @@
         <v>2.8276</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5189</v>
+        <v>-0.989</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7498</v>
+        <v>-0.9734</v>
       </c>
       <c r="U22" t="n">
-        <v>0.231</v>
+        <v>-0.0156</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4552</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.5502</v>
+        <v>-7.0903</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0478</v>
+        <v>-5.8243</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5024</v>
+        <v>-1.266</v>
       </c>
       <c r="G23" t="n">
         <v>-4.551</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3461</v>
+        <v>-0.8862</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9469</v>
+        <v>-0.7234</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3992</v>
+        <v>-0.1628</v>
       </c>
       <c r="V23" t="n">
         <v>0.7395</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.727899999999998</v>
+        <v>-7.237800000000002</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.0716</v>
+        <v>-2.071500000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.656499999999999</v>
+        <v>-5.1662</v>
       </c>
       <c r="G24" t="n">
         <v>-9.1004</v>
@@ -2326,13 +2326,13 @@
         <v>18.4881</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.459899999999999</v>
+        <v>-6.969799999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.858900000000001</v>
+        <v>-7.8591</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.601</v>
+        <v>0.8890999999999998</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9555000000000002</v>
